--- a/healthcare_surveys/050_obesity_quiz--healthcare_surveys.xlsx
+++ b/healthcare_surveys/050_obesity_quiz--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,87 +520,87 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>demographic_info</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>demographic_info</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>height_and_weight</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>height_and_weight</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>waist_circumference</t>
+          <t>education_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>waist_circumference</t>
+          <t>Education Level</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +612,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>height</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi</t>
+          <t>height_unit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi</t>
+          <t>Height Unit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>body_mass_category</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>body_mass_category</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi_category</t>
+          <t>weight_unit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi_category</t>
+          <t>Weight Unit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>waist_circumference</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Waist Circumference</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +727,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>height_unit</t>
+          <t>waist_circumference_unit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>height_unit</t>
+          <t>Waist Circumference Unit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>weight_unit</t>
+          <t>body_mass_index_bmi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>weight_unit</t>
+          <t>Body Mass Index (BMI)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,41 +773,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>waist_circumference_unit</t>
+          <t>body_mass_category</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>waist_circumference_unit</t>
+          <t>Body Mass Category</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,58 +819,58 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>smoking_status</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>Smoking Status</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ethnicity</t>
+          <t>income</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ethnicity</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>education_level</t>
+          <t>income_frequency</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>education_level</t>
+          <t>Income Frequency</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,195 +893,80 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>marital_status</t>
+          <t>Marital Status</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>income_frequency_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>Income Frequency 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>ethnicity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>income_frequency</t>
+          <t>smoking_status_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>income_frequency</t>
+          <t>Smoking Status 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>smoking_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>smoking_status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>waist_circumference</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>waist_circumference</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>body_mass_index_bmi</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>body_mass_index_bmi</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +983,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,204 +1011,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>body_mass_category_choices</t>
+          <t>sex_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>underweight</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Underweight</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>body_mass_category_choices</t>
+          <t>sex_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>body_mass_category_choices</t>
+          <t>sex_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>overweight</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Overweight</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>body_mass_category_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>obese_class_1</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Obese Class 1</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>body_mass_category_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>obese_class_2</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Obese Class 2</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>body_mass_category_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>obese_class_3</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Obese Class 3</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi_category_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>underweight</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Underweight</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi_category_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>master's_or_more</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Master's or more</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi_category_choices</t>
+          <t>occupation_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>overweight</t>
+          <t>healthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Overweight</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi_category_choices</t>
+          <t>occupation_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>obese_class_1</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Obese Class 1</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi_category_choices</t>
+          <t>occupation_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>obese_class_2</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Obese Class 2</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>body_mass_index_bmi_category_choices</t>
+          <t>occupation_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>obese_class_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Obese Class 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1483,238 +1368,238 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sex_choices</t>
+          <t>body_mass_category_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>underweight</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Underweight</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sex_choices</t>
+          <t>body_mass_category_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sex_choices</t>
+          <t>body_mass_category_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>overweight</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Overweight</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>body_mass_category_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>african_american</t>
+          <t>obese_class_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>African American</t>
+          <t>Obese Class 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>body_mass_category_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>american_indian</t>
+          <t>obese_class_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>American Indian</t>
+          <t>Obese Class 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>body_mass_category_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>asian</t>
+          <t>obese_class_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Asian</t>
+          <t>Obese Class 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>smoking_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>black_or_african_american</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Black or African American</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>smoking_status_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>former</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Former</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>smoking_status_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>current</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Current</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High school</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>some_college</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Some college</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bachelor's_degree</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bachelor's degree</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>master's_or_more</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Master's or more</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1611,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1628,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1760,214 +1645,146 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>divorced</t>
+          <t>separated</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Divorced</t>
+          <t>Separated</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>marital_status_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>widowed</t>
+          <t>african_american</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Widowed</t>
+          <t>African American</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>marital_status_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>separated</t>
+          <t>american_indian</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Separated</t>
+          <t>American Indian</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>occupation_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>healthcare</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>occupation_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>occupation_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>student</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>occupation_choices</t>
+          <t>smoking_status_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_frequency_choices</t>
+          <t>smoking_status_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>former</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Former</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_frequency_choices</t>
+          <t>smoking_status_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>current</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>income_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>smoking_status_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>smoking_status_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>former</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Former</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>smoking_status_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
